--- a/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/ssza_vorlage.xlsx
+++ b/java/bundles/org.eclipse.set.feature/rootdir/data/export/excel/ssza_vorlage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ws_intern\planpro\set\java\bundles\org.eclipse.set.feature\rootdir\data\export\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14A779BF-3D10-4F67-A2A0-6EDB0E7EA062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA2FCC3F-9C62-4F1F-A912-EDAB6EA7FA67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ssza" sheetId="1" r:id="rId1"/>
@@ -482,7 +482,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -576,40 +576,7 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -620,6 +587,59 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="17" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1003,26 +1023,26 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="23"/>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="41" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="41" t="s">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="43"/>
+      <c r="G2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="H2" s="42"/>
-      <c r="I2" s="43"/>
-      <c r="J2" s="41" t="s">
+      <c r="H2" s="31"/>
+      <c r="I2" s="32"/>
+      <c r="J2" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
-      <c r="N2" s="43"/>
-      <c r="O2" s="29" t="s">
+      <c r="K2" s="31"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="33" t="s">
         <v>31</v>
       </c>
       <c r="P2" s="35" t="s">
@@ -1031,66 +1051,66 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="32" t="s">
+      <c r="C3" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="D3" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="E3" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="33" t="s">
+      <c r="F3" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="38" t="s">
         <v>23</v>
       </c>
-      <c r="I3" s="33"/>
-      <c r="J3" s="31" t="s">
+      <c r="I3" s="39"/>
+      <c r="J3" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="K3" s="32" t="s">
+      <c r="K3" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="L3" s="32" t="s">
+      <c r="L3" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="M3" s="32" t="s">
+      <c r="M3" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="N3" s="33" t="s">
+      <c r="N3" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="O3" s="30"/>
+      <c r="O3" s="34"/>
       <c r="P3" s="36"/>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="23"/>
-      <c r="B4" s="31"/>
-      <c r="C4" s="32"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="32"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="31"/>
+      <c r="B4" s="37"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="37"/>
       <c r="H4" s="11" t="s">
         <v>26</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="J4" s="31"/>
-      <c r="K4" s="32"/>
-      <c r="L4" s="34"/>
-      <c r="M4" s="32"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="30"/>
+      <c r="J4" s="37"/>
+      <c r="K4" s="38"/>
+      <c r="L4" s="40"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="34"/>
       <c r="P4" s="36"/>
     </row>
     <row r="5" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1113,42 +1133,42 @@
       <c r="O5" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="P5" s="37"/>
+      <c r="P5" s="29"/>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="23"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
       <c r="D6" s="16"/>
       <c r="E6" s="16"/>
       <c r="F6" s="17"/>
-      <c r="G6" s="16"/>
+      <c r="G6" s="18"/>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="16"/>
-      <c r="L6" s="16"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
       <c r="M6" s="16"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
       <c r="P6" s="24"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="25"/>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
       <c r="D7" s="26"/>
       <c r="E7" s="26"/>
       <c r="F7" s="27"/>
-      <c r="G7" s="26"/>
+      <c r="G7" s="44"/>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
+      <c r="J7" s="46"/>
+      <c r="K7" s="44"/>
+      <c r="L7" s="44"/>
       <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
-      <c r="O7" s="26"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="48"/>
       <c r="P7" s="28"/>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
@@ -1739,6 +1759,7 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="J2:N2"/>
     <mergeCell ref="O2:O4"/>
     <mergeCell ref="P2:P4"/>
@@ -1755,7 +1776,6 @@
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
     <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G2:I2"/>
   </mergeCells>
   <pageMargins left="0.78740157480314965" right="0.39370078740157483" top="0.19685039370078741" bottom="0.59055118110236227" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="8" orientation="landscape" r:id="rId1"/>
